--- a/erp-server/erp-server-plm/src/main/resources/excel/productCertificate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productCertificate.xlsx
@@ -29,9 +29,16 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -50,6 +57,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -65,6 +79,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -80,6 +101,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -116,6 +144,9 @@
   </si>
   <si>
     <t>{.dictProjectName}</t>
+  </si>
+  <si>
+    <t>{.attachName}</t>
   </si>
   <si>
     <t>{.certificateValidTime}</t>
@@ -1128,19 +1159,19 @@
         <v>12</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
